--- a/output/Single/NR-AR/results.xlsx
+++ b/output/Single/NR-AR/results.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -766,6 +766,117 @@
         <v>0.8940852880477905</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>&lt;Sequential name=sequential, built=True&gt;</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TOX21-NR_AR</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>[512, 256, 128, 64]</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ReLU + Sigmoid</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>[[5364  201]
+ [   0 5565]]</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>[[667  28]
+ [ 19  12]]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>[[641  55]
+ [ 12  19]]</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.06805060803890228</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.2262723445892334</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.3131101727485657</v>
+      </c>
+      <c r="M4" t="n">
+        <v>200</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1024</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              precision    recall  f1-score   support
+         0.0       1.00      0.96      0.98      5565
+         1.0       0.97      1.00      0.98      5565
+    accuracy                           0.98     11130
+   macro avg       0.98      0.98      0.98     11130
+weighted avg       0.98      0.98      0.98     11130
+</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              precision    recall  f1-score   support
+         0.0       0.97      0.96      0.97       695
+         1.0       0.30      0.39      0.34        31
+    accuracy                           0.94       726
+   macro avg       0.64      0.67      0.65       726
+weighted avg       0.94      0.94      0.94       726
+</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              precision    recall  f1-score   support
+         0.0       0.98      0.92      0.95       696
+         1.0       0.26      0.61      0.36        31
+    accuracy                           0.91       727
+   macro avg       0.62      0.77      0.66       727
+weighted avg       0.95      0.91      0.93       727
+</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>&lt;keras.src.optimizers.adam.Adam object at 0x000001A19D95CE60&gt;</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>0.9819406867027283</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.9352617263793945</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.9078404307365417</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
